--- a/OAT/Lab11.xlsx
+++ b/OAT/Lab11.xlsx
@@ -2,24 +2,28 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
+  <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Btech\3rdSem\OAT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9F8CB58-F6C9-4DFB-8B76-ED0FC1569C30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E4E3645-56C7-49F8-B064-AD96F94D2C77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{5F6A0881-58CC-46B1-84CD-E362E04865B4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{5F6A0881-58CC-46B1-84CD-E362E04865B4}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId2"/>
-    <sheet name="Sheet4" sheetId="4" r:id="rId3"/>
-    <sheet name="Sheet6" sheetId="6" r:id="rId4"/>
-    <sheet name="Sheet5" sheetId="5" r:id="rId5"/>
+    <sheet name="Pivot,slicer,chart" sheetId="1" r:id="rId1"/>
+    <sheet name="Pivot,slicer,chart2" sheetId="3" r:id="rId2"/>
+    <sheet name="Pivot,slicer,chart3" sheetId="4" r:id="rId3"/>
+    <sheet name="XLOOKUP,INDEX,MATCH" sheetId="6" r:id="rId4"/>
+    <sheet name="Attendence System" sheetId="5" r:id="rId5"/>
+    <sheet name="Cascade Drop-Down" sheetId="7" r:id="rId6"/>
+    <sheet name="Calender" sheetId="8" r:id="rId7"/>
   </sheets>
   <definedNames>
+    <definedName name="CA">'Cascade Drop-Down'!$A$2:$A$8</definedName>
+    <definedName name="CB">'Cascade Drop-Down'!$B$2:$B$8</definedName>
     <definedName name="Slicer_Category">#N/A</definedName>
     <definedName name="Slicer_Region">#N/A</definedName>
     <definedName name="Slicer_Region1">#N/A</definedName>
@@ -29,19 +33,19 @@
   </definedNames>
   <calcPr calcId="181029"/>
   <pivotCaches>
-    <pivotCache cacheId="6" r:id="rId6"/>
-    <pivotCache cacheId="11" r:id="rId7"/>
-    <pivotCache cacheId="17" r:id="rId8"/>
+    <pivotCache cacheId="0" r:id="rId8"/>
+    <pivotCache cacheId="1" r:id="rId9"/>
+    <pivotCache cacheId="2" r:id="rId10"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
       <x14:slicerCaches>
-        <x14:slicerCache r:id="rId9"/>
-        <x14:slicerCache r:id="rId10"/>
         <x14:slicerCache r:id="rId11"/>
         <x14:slicerCache r:id="rId12"/>
         <x14:slicerCache r:id="rId13"/>
         <x14:slicerCache r:id="rId14"/>
+        <x14:slicerCache r:id="rId15"/>
+        <x14:slicerCache r:id="rId16"/>
       </x14:slicerCaches>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
@@ -55,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="145">
   <si>
     <t>Product ID</t>
   </si>
@@ -451,13 +455,52 @@
   </si>
   <si>
     <t>P</t>
+  </si>
+  <si>
+    <t>CA</t>
+  </si>
+  <si>
+    <t>CB</t>
+  </si>
+  <si>
+    <t>Select Class</t>
+  </si>
+  <si>
+    <t>Student</t>
+  </si>
+  <si>
+    <t>MONTH</t>
+  </si>
+  <si>
+    <t>YEAR</t>
+  </si>
+  <si>
+    <t>SUN</t>
+  </si>
+  <si>
+    <t>MON</t>
+  </si>
+  <si>
+    <t>TUE</t>
+  </si>
+  <si>
+    <t>WED</t>
+  </si>
+  <si>
+    <t>THU</t>
+  </si>
+  <si>
+    <t>FRI</t>
+  </si>
+  <si>
+    <t>SAT</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -485,6 +528,14 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -533,7 +584,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
@@ -548,19 +599,49 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="7">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="dashDotDot">
+          <color auto="1"/>
+        </left>
+        <right style="dashDotDot">
+          <color auto="1"/>
+        </right>
+        <top style="dashDotDot">
+          <color auto="1"/>
+        </top>
+        <bottom style="dashDotDot">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -578,26 +659,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -658,7 +719,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Lab11.xlsx]Sheet1!PivotTable1</c:name>
+    <c:name>[Lab11.xlsx]Pivot,slicer,chart!PivotTable1</c:name>
     <c:fmtId val="2"/>
   </c:pivotSource>
   <c:chart>
@@ -772,7 +833,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$M$3</c:f>
+              <c:f>'Pivot,slicer,chart'!$M$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -793,7 +854,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$L$4:$L$9</c:f>
+              <c:f>'Pivot,slicer,chart'!$L$4:$L$9</c:f>
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
@@ -816,7 +877,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$M$4:$M$9</c:f>
+              <c:f>'Pivot,slicer,chart'!$M$4:$M$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -1077,7 +1138,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Lab11.xlsx]Sheet3!PivotTable2</c:name>
+    <c:name>[Lab11.xlsx]Pivot,slicer,chart2!PivotTable2</c:name>
     <c:fmtId val="1"/>
   </c:pivotSource>
   <c:chart>
@@ -1181,7 +1242,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet3!$K$2</c:f>
+              <c:f>'Pivot,slicer,chart2'!$K$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1202,7 +1263,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet3!$J$3:$J$8</c:f>
+              <c:f>'Pivot,slicer,chart2'!$J$3:$J$8</c:f>
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
@@ -1225,7 +1286,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet3!$K$3:$K$8</c:f>
+              <c:f>'Pivot,slicer,chart2'!$K$3:$K$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -1486,7 +1547,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Lab11.xlsx]Sheet4!PivotTable3</c:name>
+    <c:name>[Lab11.xlsx]Pivot,slicer,chart3!PivotTable3</c:name>
     <c:fmtId val="1"/>
   </c:pivotSource>
   <c:chart>
@@ -1590,7 +1651,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet4!$K$2</c:f>
+              <c:f>'Pivot,slicer,chart3'!$K$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1611,7 +1672,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet4!$J$3:$J$8</c:f>
+              <c:f>'Pivot,slicer,chart3'!$J$3:$J$8</c:f>
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
@@ -1634,7 +1695,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet4!$K$3:$K$8</c:f>
+              <c:f>'Pivot,slicer,chart3'!$K$3:$K$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -3561,8 +3622,8 @@
       <xdr:row>8</xdr:row>
       <xdr:rowOff>142875</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="5" name="Region">
@@ -3585,7 +3646,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -3639,8 +3700,8 @@
       <xdr:row>8</xdr:row>
       <xdr:rowOff>180975</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="6" name="Units Sold">
@@ -3663,7 +3724,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -3722,8 +3783,8 @@
       <xdr:row>7</xdr:row>
       <xdr:rowOff>361950</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="2" name="Category">
@@ -3746,7 +3807,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -3800,8 +3861,8 @@
       <xdr:row>7</xdr:row>
       <xdr:rowOff>314325</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="3" name="Total Revenue ($)">
@@ -3824,7 +3885,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -3919,8 +3980,8 @@
       <xdr:row>13</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="2" name="Region 1">
@@ -3943,7 +4004,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -3997,8 +4058,8 @@
       <xdr:row>13</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="3" name="Total Revenue ($) 1">
@@ -4021,7 +4082,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -4104,7 +4165,7 @@
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="student" refreshedDate="46251.52180451389" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="15" xr:uid="{2B30E63C-4C47-44E5-8392-83436876EA8A}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:H16" sheet="Sheet1"/>
+    <worksheetSource ref="A1:H16" sheet="Pivot,slicer,chart"/>
   </cacheSource>
   <cacheFields count="8">
     <cacheField name="Product ID" numFmtId="0">
@@ -4187,7 +4248,7 @@
 <file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="student" refreshedDate="46251.526897685188" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="15" xr:uid="{83F2A1AF-5285-49CD-B144-63CBB36FCFA7}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:H16" sheet="Sheet3"/>
+    <worksheetSource ref="A1:H16" sheet="Pivot,slicer,chart2"/>
   </cacheSource>
   <cacheFields count="8">
     <cacheField name="Product ID" numFmtId="0">
@@ -4247,7 +4308,7 @@
 <file path=xl/pivotCache/pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="student" refreshedDate="46251.527869791666" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="15" xr:uid="{C763B2A0-9665-4331-9A8E-7BCAF58F813F}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:H16" sheet="Sheet4"/>
+    <worksheetSource ref="A1:H16" sheet="Pivot,slicer,chart3"/>
   </cacheSource>
   <cacheFields count="8">
     <cacheField name="Product ID" numFmtId="0">
@@ -4770,7 +4831,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{004433EE-62E3-4113-B150-5FF936DD5D03}" name="PivotTable1" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{004433EE-62E3-4113-B150-5FF936DD5D03}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
   <location ref="L3:M9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField showAll="0"/>
@@ -4891,7 +4952,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7ABF9E96-BD9C-4298-8B9E-D257477FBF0A}" name="PivotTable2" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7ABF9E96-BD9C-4298-8B9E-D257477FBF0A}" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
   <location ref="J2:K8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField showAll="0"/>
@@ -4983,7 +5044,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{764EFA51-1820-4795-A014-68F982C624F9}" name="PivotTable3" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{764EFA51-1820-4795-A014-68F982C624F9}" name="PivotTable3" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
   <location ref="J2:K8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField showAll="0"/>
@@ -5534,6 +5595,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5674AA83-690A-47E4-96F8-C81B508EE5E3}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:M16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5660,7 +5722,7 @@
       <c r="L4" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="M4" s="6">
+      <c r="M4">
         <v>2300</v>
       </c>
     </row>
@@ -5692,7 +5754,7 @@
       <c r="L5" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="M5" s="6">
+      <c r="M5">
         <v>640</v>
       </c>
     </row>
@@ -5724,7 +5786,7 @@
       <c r="L6" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="M6" s="6">
+      <c r="M6">
         <v>1540</v>
       </c>
     </row>
@@ -5756,7 +5818,7 @@
       <c r="L7" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="M7" s="6">
+      <c r="M7">
         <v>65</v>
       </c>
     </row>
@@ -5788,7 +5850,7 @@
       <c r="L8" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M8" s="6">
+      <c r="M8">
         <v>4790</v>
       </c>
     </row>
@@ -5820,7 +5882,7 @@
       <c r="L9" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="M9" s="6">
+      <c r="M9">
         <v>9335</v>
       </c>
     </row>
@@ -6022,6 +6084,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2483DBBD-BBC2-4A93-A5B1-D6D92445829C}">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6123,7 +6186,7 @@
       <c r="J3" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="K3" s="6">
+      <c r="K3">
         <v>1</v>
       </c>
     </row>
@@ -6155,7 +6218,7 @@
       <c r="J4" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4">
         <v>4</v>
       </c>
     </row>
@@ -6187,7 +6250,7 @@
       <c r="J5" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="K5" s="6">
+      <c r="K5">
         <v>3</v>
       </c>
     </row>
@@ -6219,7 +6282,7 @@
       <c r="J6" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K6">
         <v>3</v>
       </c>
     </row>
@@ -6251,7 +6314,7 @@
       <c r="J7" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="K7" s="6">
+      <c r="K7">
         <v>4</v>
       </c>
     </row>
@@ -6283,7 +6346,7 @@
       <c r="J8" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="K8" s="6">
+      <c r="K8">
         <v>15</v>
       </c>
     </row>
@@ -6510,6 +6573,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35101E7F-7988-4D69-AC06-BDB954004AB2}">
+  <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6611,7 +6675,7 @@
       <c r="J3" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="6">
+      <c r="K3">
         <v>3</v>
       </c>
     </row>
@@ -6643,7 +6707,7 @@
       <c r="J4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4">
         <v>3</v>
       </c>
     </row>
@@ -6675,7 +6739,7 @@
       <c r="J5" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="K5" s="6">
+      <c r="K5">
         <v>3</v>
       </c>
     </row>
@@ -6707,7 +6771,7 @@
       <c r="J6" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K6">
         <v>1</v>
       </c>
     </row>
@@ -6739,7 +6803,7 @@
       <c r="J7" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="K7" s="6">
+      <c r="K7">
         <v>5</v>
       </c>
     </row>
@@ -6771,7 +6835,7 @@
       <c r="J8" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="K8" s="6">
+      <c r="K8">
         <v>15</v>
       </c>
     </row>
@@ -6998,6 +7062,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89331FD4-2F10-4FFC-82AC-A6A20BAACD63}">
+  <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:O6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -7029,20 +7094,20 @@
       <c r="F1" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9" t="s">
+      <c r="L1" s="8"/>
+      <c r="M1" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="O1" s="8" t="s">
         <v>113</v>
       </c>
     </row>
@@ -7211,6 +7276,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{758F44A4-7613-43DE-AF55-262780B123D4}">
+  <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:P16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -7218,7 +7284,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>95</v>
       </c>
       <c r="B1">
@@ -8019,11 +8085,11 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:P16">
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
       <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
-      <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
@@ -8033,4 +8099,347 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{666B2A91-240D-4B7E-8B2E-561CB6FF1FB0}">
+  <sheetPr codeName="Sheet6"/>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="12.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B5" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>119</v>
+      </c>
+      <c r="B6" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>120</v>
+      </c>
+      <c r="B7" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>121</v>
+      </c>
+      <c r="B8" t="s">
+        <v>128</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:B8">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>A1&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2" xr:uid="{4D1C6208-CE91-432A-955E-CD79AB4256A6}">
+      <formula1>"CA,CB"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2" xr:uid="{5EED0C84-EDD6-49D9-9D81-3AE96B269FC7}">
+      <formula1>INDIRECT($D$2)</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8749C10-9956-4F3D-8046-4CB420DEC14A}">
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" customWidth="1"/>
+    <col min="6" max="7" width="11.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B2">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="9">
+        <f>DATE(B2,B1,1)-WEEKDAY(DATE(B2,B1,1),1)+1</f>
+        <v>46229</v>
+      </c>
+      <c r="B5" s="9">
+        <f>A5+1</f>
+        <v>46230</v>
+      </c>
+      <c r="C5" s="9">
+        <f>B5+1</f>
+        <v>46231</v>
+      </c>
+      <c r="D5" s="9">
+        <f>C5+1</f>
+        <v>46232</v>
+      </c>
+      <c r="E5" s="9">
+        <f t="shared" ref="E5:G5" si="0">D5+1</f>
+        <v>46233</v>
+      </c>
+      <c r="F5" s="9">
+        <f t="shared" si="0"/>
+        <v>46234</v>
+      </c>
+      <c r="G5" s="9">
+        <f t="shared" si="0"/>
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="9">
+        <f>G5+1</f>
+        <v>46236</v>
+      </c>
+      <c r="B6" s="9">
+        <f>A6+1</f>
+        <v>46237</v>
+      </c>
+      <c r="C6" s="9">
+        <f t="shared" ref="C6:G6" si="1">B6+1</f>
+        <v>46238</v>
+      </c>
+      <c r="D6" s="9">
+        <f t="shared" si="1"/>
+        <v>46239</v>
+      </c>
+      <c r="E6" s="9">
+        <f t="shared" si="1"/>
+        <v>46240</v>
+      </c>
+      <c r="F6" s="9">
+        <f t="shared" si="1"/>
+        <v>46241</v>
+      </c>
+      <c r="G6" s="9">
+        <f t="shared" si="1"/>
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="9">
+        <f t="shared" ref="A7:A10" si="2">G6+1</f>
+        <v>46243</v>
+      </c>
+      <c r="B7" s="9">
+        <f t="shared" ref="B7:G7" si="3">A7+1</f>
+        <v>46244</v>
+      </c>
+      <c r="C7" s="9">
+        <f t="shared" si="3"/>
+        <v>46245</v>
+      </c>
+      <c r="D7" s="9">
+        <f t="shared" si="3"/>
+        <v>46246</v>
+      </c>
+      <c r="E7" s="9">
+        <f t="shared" si="3"/>
+        <v>46247</v>
+      </c>
+      <c r="F7" s="9">
+        <f t="shared" si="3"/>
+        <v>46248</v>
+      </c>
+      <c r="G7" s="9">
+        <f t="shared" si="3"/>
+        <v>46249</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="9">
+        <f t="shared" si="2"/>
+        <v>46250</v>
+      </c>
+      <c r="B8" s="9">
+        <f t="shared" ref="B8:G8" si="4">A8+1</f>
+        <v>46251</v>
+      </c>
+      <c r="C8" s="9">
+        <f t="shared" si="4"/>
+        <v>46252</v>
+      </c>
+      <c r="D8" s="9">
+        <f t="shared" si="4"/>
+        <v>46253</v>
+      </c>
+      <c r="E8" s="9">
+        <f t="shared" si="4"/>
+        <v>46254</v>
+      </c>
+      <c r="F8" s="9">
+        <f t="shared" si="4"/>
+        <v>46255</v>
+      </c>
+      <c r="G8" s="9">
+        <f t="shared" si="4"/>
+        <v>46256</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="9">
+        <f t="shared" si="2"/>
+        <v>46257</v>
+      </c>
+      <c r="B9" s="9">
+        <f t="shared" ref="B9:G9" si="5">A9+1</f>
+        <v>46258</v>
+      </c>
+      <c r="C9" s="9">
+        <f t="shared" si="5"/>
+        <v>46259</v>
+      </c>
+      <c r="D9" s="9">
+        <f t="shared" si="5"/>
+        <v>46260</v>
+      </c>
+      <c r="E9" s="9">
+        <f t="shared" si="5"/>
+        <v>46261</v>
+      </c>
+      <c r="F9" s="9">
+        <f t="shared" si="5"/>
+        <v>46262</v>
+      </c>
+      <c r="G9" s="9">
+        <f t="shared" si="5"/>
+        <v>46263</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="9">
+        <f t="shared" si="2"/>
+        <v>46264</v>
+      </c>
+      <c r="B10" s="9">
+        <f t="shared" ref="B10:G10" si="6">A10+1</f>
+        <v>46265</v>
+      </c>
+      <c r="C10" s="9">
+        <f t="shared" si="6"/>
+        <v>46266</v>
+      </c>
+      <c r="D10" s="9">
+        <f t="shared" si="6"/>
+        <v>46267</v>
+      </c>
+      <c r="E10" s="9">
+        <f t="shared" si="6"/>
+        <v>46268</v>
+      </c>
+      <c r="F10" s="9">
+        <f t="shared" si="6"/>
+        <v>46269</v>
+      </c>
+      <c r="G10" s="9">
+        <f t="shared" si="6"/>
+        <v>46270</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A5:G10">
+    <cfRule type="timePeriod" dxfId="0" priority="1" timePeriod="thisMonth">
+      <formula>AND(MONTH(A5)=MONTH(TODAY()),YEAR(A5)=YEAR(TODAY()))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>